--- a/QCM7_1_MATH.xlsx
+++ b/QCM7_1_MATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34004D26-B557-41FB-802E-146C0648A624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53E2EDF-39C4-4AD7-80E7-39E66C80E2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -186,7 +186,7 @@
     <t>\int_{\ln 2}^{\ln 3} \frac{e^t+e^{-t}}{e^t-e^{-t}} dt</t>
   </si>
   <si>
-    <t>$\int_{0}^{1} \frac{1}{t^2-t-2} \,\mathrm{d}t$</t>
+    <t>$\frac{1}{8}(\sin 3 \theta+3 \sin \theta)$</t>
   </si>
 </sst>
 </file>

--- a/QCM7_1_MATH.xlsx
+++ b/QCM7_1_MATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53E2EDF-39C4-4AD7-80E7-39E66C80E2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9ABFA5-DDDA-4F9D-91CC-4C059AD95C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,16 +177,16 @@
     <t>$e - 1$</t>
   </si>
   <si>
-    <t>Calculer : \left( \int_{1}^{e} t\ln(t)dt ; \int_{1}^{e} \frac{\ln(t)}{t^2}dt ; \int_{1}^{e^2} \sqrt{t}\ln(t)dt \right)</t>
-  </si>
-  <si>
-    <t>\int_{-\frac{\pi}{6}}^{\frac{\pi}{6}} \sin^7(t) dt</t>
-  </si>
-  <si>
-    <t>\int_{\ln 2}^{\ln 3} \frac{e^t+e^{-t}}{e^t-e^{-t}} dt</t>
-  </si>
-  <si>
     <t>$\frac{1}{8}(\sin 3 \theta+3 \sin \theta)$</t>
+  </si>
+  <si>
+    <t>Calculer :$ \left( \int_{1}^{e} t\ln(t)dt$ ;$ \int_{1}^{e} \frac{\ln(t)}{t^2}dt$ ; $\int_{1}^{e^2} \sqrt{t}\ln(t)dt \right)$</t>
+  </si>
+  <si>
+    <t>$\int_{-\frac{\pi}{6}}^{\frac{\pi}{6}} \sin^7(t) dt$</t>
+  </si>
+  <si>
+    <t>$\int_{\ln 2}^{\ln 3} \frac{e^t+e^{-t}}{e^t-e^{-t}} dt$</t>
   </si>
 </sst>
 </file>
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -707,7 +707,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -734,7 +734,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -761,7 +761,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>

--- a/QCM7_1_MATH.xlsx
+++ b/QCM7_1_MATH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9ABFA5-DDDA-4F9D-91CC-4C059AD95C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C81D0C5-D22E-4E10-ABB8-2F7BC1C74B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
   <si>
     <t>Question</t>
   </si>
@@ -177,9 +177,6 @@
     <t>$e - 1$</t>
   </si>
   <si>
-    <t>$\frac{1}{8}(\sin 3 \theta+3 \sin \theta)$</t>
-  </si>
-  <si>
     <t>Calculer :$ \left( \int_{1}^{e} t\ln(t)dt$ ;$ \int_{1}^{e} \frac{\ln(t)}{t^2}dt$ ; $\int_{1}^{e^2} \sqrt{t}\ln(t)dt \right)$</t>
   </si>
   <si>
@@ -187,6 +184,12 @@
   </si>
   <si>
     <t>$\int_{\ln 2}^{\ln 3} \frac{e^t+e^{-t}}{e^t-e^{-t}} dt$</t>
+  </si>
+  <si>
+    <t>L'intégrale $\int_{0}^{1}\frac{1}{t^{2}-t-2} dt$ vaut :</t>
+  </si>
+  <si>
+    <t>OptionE</t>
   </si>
 </sst>
 </file>
@@ -632,18 +635,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125"/>
     <col min="2" max="2" width="50" customWidth="1"/>
     <col min="3" max="3" width="30.42578125" customWidth="1"/>
-    <col min="4" max="7" width="35" customWidth="1"/>
-    <col min="8" max="9" width="33.140625" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="4" max="8" width="35" customWidth="1"/>
+    <col min="9" max="10" width="33.140625" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -665,22 +668,25 @@
       <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -697,17 +703,18 @@
       <c r="G2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="8"/>
+      <c r="I2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -724,17 +731,18 @@
       <c r="G3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="9"/>
+      <c r="I3" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -751,17 +759,18 @@
       <c r="G4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="8"/>
+      <c r="I4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -778,12 +787,13 @@
       <c r="G5" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="9"/>
+      <c r="I5" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J5" s="5"/>
+    </row>
+    <row r="6" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -805,12 +815,13 @@
       <c r="G6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="8"/>
+      <c r="I6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -832,12 +843,13 @@
       <c r="G7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="9"/>
+      <c r="I7" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -859,12 +871,13 @@
       <c r="G8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="8"/>
+      <c r="I8" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
@@ -886,12 +899,13 @@
       <c r="G9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="11" t="s">
+      <c r="H9" s="9"/>
+      <c r="I9" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -913,12 +927,13 @@
       <c r="G10" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="8"/>
+      <c r="I10" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:10" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>11</v>
       </c>
@@ -940,10 +955,11 @@
       <c r="G11" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="9"/>
+      <c r="I11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/QCM7_1_MATH.xlsx
+++ b/QCM7_1_MATH.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C81D0C5-D22E-4E10-ABB8-2F7BC1C74B0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65B817B-1D73-4CB2-AC5F-BE90CE0AA3C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="QCM_Intégrale" sheetId="1" r:id="rId1"/>
+    <sheet name="QCM_Intégrales" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="110">
   <si>
     <t>Question</t>
   </si>
@@ -60,136 +60,301 @@
     <t>Image</t>
   </si>
   <si>
-    <t>Chapitre V : Intégrales</t>
-  </si>
-  <si>
-    <t>$\int_{0}^{2\pi} \cos(2x)\cos(3x) dx$</t>
-  </si>
-  <si>
-    <t>$\int_{0}^{\pi} e^{3x}\cos(2x) dx$</t>
-  </si>
-  <si>
-    <t>$\int_{0}^{\pi} \sin(x)\cos(2x) dx$</t>
-  </si>
-  <si>
-    <t>$\int_{0}^{\pi} \sin(2x)\cos(x) dx$</t>
-  </si>
-  <si>
-    <t>Valeur moyenne de $\sin(x)\cos(2x)$ sur $[0, \pi]$</t>
-  </si>
-  <si>
-    <t>Aire de la partie limitée par les courbes $f(x)=x^2 e^x$ et $g(x)=(x-2)e^x$, sur $[0, 1]$</t>
-  </si>
-  <si>
     <t>$0$</t>
   </si>
   <si>
-    <t>$\ln\left(\frac{1}{2}\right)$</t>
-  </si>
-  <si>
-    <t>$-\frac{2}{3}\ln(2)$</t>
-  </si>
-  <si>
-    <t>$\ln(2)$</t>
-  </si>
-  <si>
-    <t>$\left( \frac{e^2+1}{4} ; \frac{e-2}{e} ; \frac{8e^3+4}{9} \right)$</t>
-  </si>
-  <si>
-    <t>$\left( \frac{e-2}{e} ; \frac{e^2+1}{4} ; \frac{8e^3+4}{9} \right)$</t>
-  </si>
-  <si>
-    <t>$\left( \frac{e^2+1}{4} ; \frac{8e^3+4}{9} ; \frac{e-2}{e} \right)$</t>
-  </si>
-  <si>
-    <t>$\left( \frac{8e^3+4}{9} ; \frac{e-2}{e} ; \frac{e^2+1}{4} \right)$</t>
-  </si>
-  <si>
     <t>$1$</t>
   </si>
   <si>
-    <t>$-1$</t>
-  </si>
-  <si>
-    <t>$(0 ; 2\ln3 ; 2\ln(3/4))$</t>
-  </si>
-  <si>
-    <t>$(\sqrt{3} ; 2\ln(3/4) ; 2\ln3)$</t>
-  </si>
-  <si>
-    <t>$2\ln\left(\frac{4}{3}\right)$</t>
-  </si>
-  <si>
-    <t>$(0 ; \sqrt{3} ; \ln3)$</t>
-  </si>
-  <si>
-    <t>$\pi$</t>
-  </si>
-  <si>
-    <t>$\frac{\pi}{5}$</t>
-  </si>
-  <si>
-    <t>$\frac{3}{13}$</t>
-  </si>
-  <si>
-    <t>$\frac{3}{13}(e-1)$</t>
-  </si>
-  <si>
-    <t>$\frac{3}{13}(e^{3\pi}-1)$</t>
-  </si>
-  <si>
     <t>$\frac{2}{3}$</t>
   </si>
   <si>
-    <t>$-\frac{2}{3}$</t>
-  </si>
-  <si>
-    <t>$\frac{5}{3}$</t>
-  </si>
-  <si>
-    <t>$\frac{1}{3}$</t>
-  </si>
-  <si>
-    <t>$\frac{3}{2}$</t>
-  </si>
-  <si>
-    <t>$\frac{4}{3}$</t>
-  </si>
-  <si>
-    <t>$\frac{3}{\pi}$</t>
-  </si>
-  <si>
-    <t>$\frac{2}{3\pi}$</t>
-  </si>
-  <si>
-    <t>$-\frac{2}{3\pi}$</t>
-  </si>
-  <si>
-    <t>$6\pi$</t>
-  </si>
-  <si>
-    <t>$1 - e$</t>
-  </si>
-  <si>
-    <t>$3e - 5$</t>
-  </si>
-  <si>
-    <t>$e - 1$</t>
-  </si>
-  <si>
-    <t>Calculer :$ \left( \int_{1}^{e} t\ln(t)dt$ ;$ \int_{1}^{e} \frac{\ln(t)}{t^2}dt$ ; $\int_{1}^{e^2} \sqrt{t}\ln(t)dt \right)$</t>
-  </si>
-  <si>
-    <t>$\int_{-\frac{\pi}{6}}^{\frac{\pi}{6}} \sin^7(t) dt$</t>
-  </si>
-  <si>
-    <t>$\int_{\ln 2}^{\ln 3} \frac{e^t+e^{-t}}{e^t-e^{-t}} dt$</t>
-  </si>
-  <si>
-    <t>L'intégrale $\int_{0}^{1}\frac{1}{t^{2}-t-2} dt$ vaut :</t>
-  </si>
-  <si>
     <t>OptionE</t>
+  </si>
+  <si>
+    <t>$6$</t>
+  </si>
+  <si>
+    <t>$4$</t>
+  </si>
+  <si>
+    <t>$9$</t>
+  </si>
+  <si>
+    <t>$8$</t>
+  </si>
+  <si>
+    <t>Chapitre VII : Probabilité</t>
+  </si>
+  <si>
+    <t>Dans un univers, on considère trois événements $A, B, C$ tels que $P(A)=0,3$, $P(B)=0,6$, $P(C)=0,7$.</t>
+  </si>
+  <si>
+    <t>On lance 3 fois une même pièce de monnaie. Le nombre de possibilités est :</t>
+  </si>
+  <si>
+    <t>La probabilité d'obtenir au moins 2 fois « pile » est :</t>
+  </si>
+  <si>
+    <t>On lance simultanément 3 pièces de monnaie. $A$ = « on obtient au moins une fois pile ». L'événement contraire est :</t>
+  </si>
+  <si>
+    <t>Probabilité d'interroger un non-fumeur sachant que c'est un homme (5H F, 15H NF) :</t>
+  </si>
+  <si>
+    <t>Les événements « interroger une femme » et « interroger un non fumeur » sont indépendants :</t>
+  </si>
+  <si>
+    <t>On donne $P(A)=0,4$, $P(B)=0,3$ et $P(A \cap B)=0,12$. Les événements $A$ et $B$ sont :</t>
+  </si>
+  <si>
+    <t>On donne $P(B)=0,1$, $P_A(B)=0,4$ et $P(A)=0,2$. Alors $P_B(A)$ est égale à :</t>
+  </si>
+  <si>
+    <t>On lance 2 dés cubiques. Probabilité d'obtenir deux numéros identiques :</t>
+  </si>
+  <si>
+    <t>On tire successivement sans remise 2 cartes (dans 32). Probabilité d'obtenir 2 cartes rouges :</t>
+  </si>
+  <si>
+    <t>Choisir 3 personnes parmi 12. Le nombre de commissions possibles est :</t>
+  </si>
+  <si>
+    <t>Groupe de 4 femmes et 8 hommes. Probabilité que la commission comporte exactement 2 femmes :</t>
+  </si>
+  <si>
+    <t>Probabilité achat strictement supérieur à 1 000 F (30/100) :</t>
+  </si>
+  <si>
+    <t>Probabilité achat strictement supérieur à 1 000 F payé en espèces (4/100) :</t>
+  </si>
+  <si>
+    <t>Probabilité achat payé par chèque ou par carte bancaire (82/100) :</t>
+  </si>
+  <si>
+    <t>Tirer 3 boules blanches simultanément (urne: 2 rouges, 5 blanches) :</t>
+  </si>
+  <si>
+    <t>A et B incompatibles, $P(A)=P(B)=0,2$. Alors $P(A \cup B)$ est :</t>
+  </si>
+  <si>
+    <t>A et B incompatibles, $P(A)=P(B)=0,2$. Alors $P(A \cap B)$ est :</t>
+  </si>
+  <si>
+    <t>2 jetons tirés simultanément (5 verts, 3 blancs, 2 rouges). Probabilité de 2 couleurs différentes :</t>
+  </si>
+  <si>
+    <t>Arbre avec $P(A)=0,5, P(\overline{A})=0,5$. Sachant $A$, $P(B)=0,1$. Sachant $\overline{A}$, $P(B)=0,3$.</t>
+  </si>
+  <si>
+    <t>A et B disjoints (incompatibles), $P(A)=0,5, P(B)=0,4$. $P(A \cup B)$ est égal à :</t>
+  </si>
+  <si>
+    <t>Toujours avec $P(A)=0,5, P(B)=0,4$. $P(\overline{A})$ est égal à :</t>
+  </si>
+  <si>
+    <t>$P(A \cup C)=1$</t>
+  </si>
+  <si>
+    <t>$P(\overline{A})=0,7$</t>
+  </si>
+  <si>
+    <t>$\overline{A}=C$</t>
+  </si>
+  <si>
+    <t>$P(A \cup B) \le 0,9$</t>
+  </si>
+  <si>
+    <t>$3!$</t>
+  </si>
+  <si>
+    <t>$\frac{3}{8}$</t>
+  </si>
+  <si>
+    <t>$\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>$1 - \frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>On n'obtient jamais « pile »</t>
+  </si>
+  <si>
+    <t>On n'obtient que des « faces »</t>
+  </si>
+  <si>
+    <t>On obtient au moins 2 fois « pile »</t>
+  </si>
+  <si>
+    <t>On n'obtient que des « piles »</t>
+  </si>
+  <si>
+    <t>$20$</t>
+  </si>
+  <si>
+    <t>$0,75$</t>
+  </si>
+  <si>
+    <t>$0,2$</t>
+  </si>
+  <si>
+    <t>$0,08$</t>
+  </si>
+  <si>
+    <t>$0,15$</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Oui sous certaines conditions</t>
+  </si>
+  <si>
+    <t>On ne peut pas savoir</t>
+  </si>
+  <si>
+    <t>indépendants</t>
+  </si>
+  <si>
+    <t>dépendants</t>
+  </si>
+  <si>
+    <t>incompatibles</t>
+  </si>
+  <si>
+    <t>On ne peut rien dire</t>
+  </si>
+  <si>
+    <t>$0,8$</t>
+  </si>
+  <si>
+    <t>$0,5$</t>
+  </si>
+  <si>
+    <t>$0,4$</t>
+  </si>
+  <si>
+    <t>$\frac{1}{216}$</t>
+  </si>
+  <si>
+    <t>$\frac{1}{1296}$</t>
+  </si>
+  <si>
+    <t>$\frac{1}{6}$</t>
+  </si>
+  <si>
+    <t>$\frac{C_6^1}{C_6^2}$</t>
+  </si>
+  <si>
+    <t>$\frac{15}{62}$</t>
+  </si>
+  <si>
+    <t>$\frac{1}{4}$</t>
+  </si>
+  <si>
+    <t>$\frac{C_{16}^2}{C_{32}^2}$</t>
+  </si>
+  <si>
+    <t>$1728$</t>
+  </si>
+  <si>
+    <t>$220$</t>
+  </si>
+  <si>
+    <t>$12 \times 11 \times 10$</t>
+  </si>
+  <si>
+    <t>$\frac{3}{120}$</t>
+  </si>
+  <si>
+    <t>$\frac{4}{55}$</t>
+  </si>
+  <si>
+    <t>$\frac{2}{11}$</t>
+  </si>
+  <si>
+    <t>$\frac{12}{55}$</t>
+  </si>
+  <si>
+    <t>$0,3$</t>
+  </si>
+  <si>
+    <t>$\frac{30}{100}$</t>
+  </si>
+  <si>
+    <t>$0,24$</t>
+  </si>
+  <si>
+    <t>$0,7$</t>
+  </si>
+  <si>
+    <t>$0,04$</t>
+  </si>
+  <si>
+    <t>$\frac{4}{18}$</t>
+  </si>
+  <si>
+    <t>$\frac{4}{30}$</t>
+  </si>
+  <si>
+    <t>$\frac{26}{30}$</t>
+  </si>
+  <si>
+    <t>$\frac{2}{80}$</t>
+  </si>
+  <si>
+    <t>$0,82$</t>
+  </si>
+  <si>
+    <t>$\frac{80}{100}$</t>
+  </si>
+  <si>
+    <t>$\frac{3!}{7!}$</t>
+  </si>
+  <si>
+    <t>$\frac{5! \times 4!}{7! \times 2!}$</t>
+  </si>
+  <si>
+    <t>$\frac{C_5^3}{C_7^3}$</t>
+  </si>
+  <si>
+    <t>$\frac{2}{7}$</t>
+  </si>
+  <si>
+    <t>$1 - \frac{C_5^2 + C_3^2 + C_2^2}{C_{10}^2}$</t>
+  </si>
+  <si>
+    <t>$\frac{2\times 3 + 2\times 5 + 3\times 5}{C_{10}^2}$</t>
+  </si>
+  <si>
+    <t>$\frac{C_2^1 \times C_3^1 \times C_5^1}{C_{10}^2}$</t>
+  </si>
+  <si>
+    <t>$1 - \frac{2\times 3\times 5}{C_{10}^2}$</t>
+  </si>
+  <si>
+    <t>$P_A(B)=0,9$</t>
+  </si>
+  <si>
+    <t>$P(\overline{A} \cap B)=0,15$</t>
+  </si>
+  <si>
+    <t>$P(A \cap B)=0,5$</t>
+  </si>
+  <si>
+    <t>$P(B)=0,2$</t>
+  </si>
+  <si>
+    <t>$0,1$</t>
+  </si>
+  <si>
+    <t>$0,9$</t>
+  </si>
+  <si>
+    <t>$0,45$</t>
   </si>
 </sst>
 </file>
@@ -635,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125"/>
@@ -669,7 +834,7 @@
         <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>8</v>
@@ -681,285 +846,609 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="8"/>
-      <c r="I2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="4"/>
-    </row>
-    <row r="3" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>23</v>
-      </c>
       <c r="F3" s="9" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="5"/>
+    </row>
+    <row r="4" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="10" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="J4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>30</v>
-      </c>
       <c r="G5" s="9" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="H5" s="9"/>
-      <c r="I5" s="11" t="s">
-        <v>30</v>
+      <c r="I5" s="9" t="s">
+        <v>50</v>
       </c>
       <c r="J5" s="5"/>
     </row>
-    <row r="6" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="8"/>
+        <v>57</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>58</v>
+      </c>
       <c r="I6" s="10" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="J6" s="4"/>
     </row>
-    <row r="7" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="11" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="H8" s="8"/>
       <c r="I8" s="10" t="s">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="11" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="J9" s="5"/>
     </row>
-    <row r="10" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="H10" s="8"/>
       <c r="I10" s="10" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:11" ht="43.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="8"/>
+      <c r="I18" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="9"/>
-      <c r="I11" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11" s="5"/>
+      <c r="E19" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="57.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="H23" s="9"/>
+      <c r="I23" s="11" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
